--- a/product_upload/packages/5/file.xlsx
+++ b/product_upload/packages/5/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR101"/>
+  <dimension ref="A1:AS101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,7 +590,7 @@
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
@@ -639,6 +639,11 @@
         </is>
       </c>
       <c r="AR1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -667,7 +672,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -820,6 +825,11 @@
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr">
         <is>
+          <t>LIVOSTIN EYE DROPS 0.5MG-ML</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
           <t>SKU-DA3C0BFE5E91</t>
         </is>
       </c>
@@ -847,7 +857,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1000,6 +1010,11 @@
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr">
         <is>
+          <t>LIVIAL 2.5MG TAB</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
           <t>SKU-3228702EEA00</t>
         </is>
       </c>
@@ -1027,7 +1042,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1190,6 +1205,11 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
+          <t>LIVAZO 4 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
           <t>SKU-96F0F7CE905C</t>
         </is>
       </c>
@@ -1217,7 +1237,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1376,6 +1396,11 @@
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr">
         <is>
+          <t>LIVAZO 2 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
           <t>SKU-980B1C5ED6F6</t>
         </is>
       </c>
@@ -1403,7 +1428,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1564,6 +1589,11 @@
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr">
         <is>
+          <t>LOCERYL 5% NAIL LACQUER</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
           <t>SKU-64CC49689198</t>
         </is>
       </c>
@@ -1591,7 +1621,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1744,6 +1774,11 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
+          <t>LONZET 30MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
           <t>SKU-6DE14458D65F</t>
         </is>
       </c>
@@ -1771,7 +1806,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1920,6 +1955,11 @@
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr">
         <is>
+          <t>LONZET 15MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
           <t>SKU-52309E700EB9</t>
         </is>
       </c>
@@ -1947,7 +1987,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2096,6 +2136,11 @@
       <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="inlineStr">
         <is>
+          <t>LOHIST 5 MG-5 ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
           <t>SKU-3EEA4EAB2632</t>
         </is>
       </c>
@@ -2123,7 +2168,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2276,6 +2321,11 @@
       <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="inlineStr">
         <is>
+          <t>LOHIST 10 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
           <t>SKU-E10E4A867E5C</t>
         </is>
       </c>
@@ -2303,7 +2353,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2456,6 +2506,11 @@
       <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="inlineStr">
         <is>
+          <t>LOFRAL 5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
           <t>SKU-62A5A9D6FC89</t>
         </is>
       </c>
@@ -2483,7 +2538,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2636,6 +2691,11 @@
       <c r="AQ12" t="inlineStr"/>
       <c r="AR12" t="inlineStr">
         <is>
+          <t>LOFRAL 10MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
           <t>SKU-E97921EE4732</t>
         </is>
       </c>
@@ -2663,7 +2723,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2812,6 +2872,11 @@
       <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="inlineStr">
         <is>
+          <t>LOCOID OINT 0.1%</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
           <t>SKU-66F4B115E212</t>
         </is>
       </c>
@@ -2839,7 +2904,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3000,6 +3065,11 @@
       <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="inlineStr">
         <is>
+          <t>LOGYNON TAB</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
           <t>SKU-5F012B1C82CE</t>
         </is>
       </c>
@@ -3027,7 +3097,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3188,6 +3258,11 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
+          <t>LISINO 5MG TABLET</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
           <t>SKU-F9BB02723BF8</t>
         </is>
       </c>
@@ -3215,7 +3290,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3368,6 +3443,11 @@
       <c r="AQ16" t="inlineStr"/>
       <c r="AR16" t="inlineStr">
         <is>
+          <t>LINOPRIL 10MG TABLET</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
           <t>SKU-193C62EE17D1</t>
         </is>
       </c>
@@ -3395,7 +3475,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3548,6 +3628,11 @@
       <c r="AQ17" t="inlineStr"/>
       <c r="AR17" t="inlineStr">
         <is>
+          <t>LEXOTANIL TAB. 3MG</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
           <t>SKU-61135CCE8778</t>
         </is>
       </c>
@@ -3575,7 +3660,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3732,6 +3817,11 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
+          <t>LINOPRIL 20MG TABLET</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
           <t>SKU-81C0C5DDA251</t>
         </is>
       </c>
@@ -3759,7 +3849,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3912,6 +4002,11 @@
       <c r="AQ19" t="inlineStr"/>
       <c r="AR19" t="inlineStr">
         <is>
+          <t>LINOPRIL 5MG TABLET</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
           <t>SKU-381060B06227</t>
         </is>
       </c>
@@ -3939,7 +4034,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4088,6 +4183,11 @@
       <c r="AQ20" t="inlineStr"/>
       <c r="AR20" t="inlineStr">
         <is>
+          <t>LINZ 20 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
           <t>SKU-835C0524FABD</t>
         </is>
       </c>
@@ -4115,7 +4215,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4268,6 +4368,11 @@
       <c r="AQ21" t="inlineStr"/>
       <c r="AR21" t="inlineStr">
         <is>
+          <t>LIOCAINE 2% GEL</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
           <t>SKU-18AC6A732736</t>
         </is>
       </c>
@@ -4295,7 +4400,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4456,6 +4561,11 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
+          <t>LISINO 20MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
           <t>SKU-55E52DF38188</t>
         </is>
       </c>
@@ -4483,7 +4593,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4644,6 +4754,11 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
+          <t>LISINO 10MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
           <t>SKU-80AE3E260C2C</t>
         </is>
       </c>
@@ -4671,7 +4786,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4832,6 +4947,11 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
+          <t>LIORESAL 25MG TAB</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
           <t>SKU-B0C31864AF50</t>
         </is>
       </c>
@@ -4859,7 +4979,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5016,6 +5136,11 @@
       <c r="AQ25" t="inlineStr"/>
       <c r="AR25" t="inlineStr">
         <is>
+          <t>LIORESAL 10MG TAB</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
           <t>SKU-45A25E949E6F</t>
         </is>
       </c>
@@ -5043,7 +5168,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5204,6 +5329,11 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
+          <t>NERVAX 75MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
           <t>SKU-D316836B4E31</t>
         </is>
       </c>
@@ -5231,7 +5361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5384,6 +5514,11 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
+          <t>NERVAX 300MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
           <t>SKU-12CE56A230A9</t>
         </is>
       </c>
@@ -5411,7 +5546,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5564,6 +5699,11 @@
       <c r="AQ28" t="inlineStr"/>
       <c r="AR28" t="inlineStr">
         <is>
+          <t>NERVAX 150MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
           <t>SKU-436FB1EC6B46</t>
         </is>
       </c>
@@ -5591,7 +5731,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5748,6 +5888,11 @@
       </c>
       <c r="AR29" t="inlineStr">
         <is>
+          <t>NEOXIDIL 2% SOLN.</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
           <t>SKU-48120A4BAB71</t>
         </is>
       </c>
@@ -5775,7 +5920,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5924,6 +6069,11 @@
       <c r="AQ30" t="inlineStr"/>
       <c r="AR30" t="inlineStr">
         <is>
+          <t>NEOXICAM 7.5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
           <t>SKU-EC361FC14CCD</t>
         </is>
       </c>
@@ -5951,7 +6101,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6096,6 +6246,11 @@
       <c r="AQ31" t="inlineStr"/>
       <c r="AR31" t="inlineStr">
         <is>
+          <t>NEOXICAM 15MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
           <t>SKU-1A38D14DD7C9</t>
         </is>
       </c>
@@ -6123,7 +6278,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6272,6 +6427,11 @@
       <c r="AQ32" t="inlineStr"/>
       <c r="AR32" t="inlineStr">
         <is>
+          <t>NEOVENTIL 2MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
           <t>SKU-4959F7C24022</t>
         </is>
       </c>
@@ -6299,7 +6459,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6452,6 +6612,11 @@
       </c>
       <c r="AR33" t="inlineStr">
         <is>
+          <t>NEOTIGASON 25MG CAPS</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
           <t>SKU-50631D6A1544</t>
         </is>
       </c>
@@ -6479,7 +6644,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6624,6 +6789,11 @@
       <c r="AQ34" t="inlineStr"/>
       <c r="AR34" t="inlineStr">
         <is>
+          <t>NEOTIGASON 10MG CAPS</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
           <t>SKU-51D681741AE1</t>
         </is>
       </c>
@@ -6651,7 +6821,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6808,6 +6978,11 @@
       <c r="AQ35" t="inlineStr"/>
       <c r="AR35" t="inlineStr">
         <is>
+          <t>NEORIN 5MG F.C. TABLET</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
           <t>SKU-0C34ACF098E2</t>
         </is>
       </c>
@@ -6835,7 +7010,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -6984,6 +7159,11 @@
       <c r="AQ36" t="inlineStr"/>
       <c r="AR36" t="inlineStr">
         <is>
+          <t>NEORIN 2.5MG -5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
           <t>SKU-044CA53B76C8</t>
         </is>
       </c>
@@ -7011,7 +7191,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7168,6 +7348,11 @@
       <c r="AQ37" t="inlineStr"/>
       <c r="AR37" t="inlineStr">
         <is>
+          <t>NEURO-B FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
           <t>SKU-6EDE3C49FC76</t>
         </is>
       </c>
@@ -7195,7 +7380,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7348,6 +7533,11 @@
       <c r="AQ38" t="inlineStr"/>
       <c r="AR38" t="inlineStr">
         <is>
+          <t>NEUROBION ampoules</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
           <t>SKU-71A7BE570168</t>
         </is>
       </c>
@@ -7375,7 +7565,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7526,6 +7716,11 @@
       </c>
       <c r="AR39" t="inlineStr">
         <is>
+          <t>NEUROTRAT FORTE TAB.</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
           <t>SKU-2D6689B0D9DF</t>
         </is>
       </c>
@@ -7553,7 +7748,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7718,6 +7913,11 @@
       </c>
       <c r="AR40" t="inlineStr">
         <is>
+          <t>NEURORUBINE-FORTE</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
           <t>SKU-116963139BE6</t>
         </is>
       </c>
@@ -7745,7 +7945,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -7902,6 +8102,11 @@
       <c r="AQ41" t="inlineStr"/>
       <c r="AR41" t="inlineStr">
         <is>
+          <t>NEOPRED - P</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
           <t>SKU-61E758FBA81C</t>
         </is>
       </c>
@@ -7929,7 +8134,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8082,6 +8287,11 @@
       <c r="AQ42" t="inlineStr"/>
       <c r="AR42" t="inlineStr">
         <is>
+          <t>NEUROPLEX 400MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
           <t>SKU-1869619FCAAD</t>
         </is>
       </c>
@@ -8109,7 +8319,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8270,6 +8480,11 @@
       </c>
       <c r="AR43" t="inlineStr">
         <is>
+          <t>NEURONTIN</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
           <t>SKU-03A775F3597D</t>
         </is>
       </c>
@@ -8297,7 +8512,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8450,6 +8665,11 @@
       <c r="AQ44" t="inlineStr"/>
       <c r="AR44" t="inlineStr">
         <is>
+          <t>NEURONTIN</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
           <t>SKU-6F377E6B1852</t>
         </is>
       </c>
@@ -8477,7 +8697,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8630,6 +8850,11 @@
       <c r="AQ45" t="inlineStr"/>
       <c r="AR45" t="inlineStr">
         <is>
+          <t>NEUROPLEX 300MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
           <t>SKU-DA3E80801267</t>
         </is>
       </c>
@@ -8657,7 +8882,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8810,6 +9035,11 @@
       </c>
       <c r="AR46" t="inlineStr">
         <is>
+          <t>NEOMOX 250MG-5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
           <t>SKU-D32384DE69FB</t>
         </is>
       </c>
@@ -8837,7 +9067,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -8986,6 +9216,11 @@
       <c r="AQ47" t="inlineStr"/>
       <c r="AR47" t="inlineStr">
         <is>
+          <t>NEOMOL 120MG-5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
           <t>SKU-0529AF3BC153</t>
         </is>
       </c>
@@ -9013,7 +9248,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9162,6 +9397,11 @@
       <c r="AQ48" t="inlineStr"/>
       <c r="AR48" t="inlineStr">
         <is>
+          <t>NAPROX D.S 500MG TAB</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
           <t>SKU-BEC66910E936</t>
         </is>
       </c>
@@ -9189,7 +9429,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9346,6 +9586,11 @@
       <c r="AQ49" t="inlineStr"/>
       <c r="AR49" t="inlineStr">
         <is>
+          <t>NAPROX 250MG TAB</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
           <t>SKU-0EE1AC1F2810</t>
         </is>
       </c>
@@ -9373,7 +9618,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9530,6 +9775,11 @@
       <c r="AQ50" t="inlineStr"/>
       <c r="AR50" t="inlineStr">
         <is>
+          <t>NAPROTEX 500 mg tablet</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
           <t>SKU-585DC596D166</t>
         </is>
       </c>
@@ -9557,7 +9807,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9718,6 +9968,11 @@
       </c>
       <c r="AR51" t="inlineStr">
         <is>
+          <t>NAPHCON-A EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
           <t>SKU-36AEE0FA0A7A</t>
         </is>
       </c>
@@ -9745,7 +10000,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -9912,6 +10167,11 @@
       </c>
       <c r="AR52" t="inlineStr">
         <is>
+          <t>NATRILIX 1.5 MG S.R TAB</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
           <t>SKU-1A767AD6F084</t>
         </is>
       </c>
@@ -9939,7 +10199,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10086,6 +10346,11 @@
       <c r="AQ53" t="inlineStr"/>
       <c r="AR53" t="inlineStr">
         <is>
+          <t>NEO-HAEMORRHAN OINT</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
           <t>SKU-ECBADF4E5E30</t>
         </is>
       </c>
@@ -10113,7 +10378,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10264,6 +10529,11 @@
       </c>
       <c r="AR54" t="inlineStr">
         <is>
+          <t>NEO-HAEMORRHAN SUPP.</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
           <t>SKU-7CE016874226</t>
         </is>
       </c>
@@ -10291,7 +10561,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10448,6 +10718,11 @@
       <c r="AQ55" t="inlineStr"/>
       <c r="AR55" t="inlineStr">
         <is>
+          <t>NEODEX 0.1 E-E DROP</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
           <t>SKU-6F9BB7363FFA</t>
         </is>
       </c>
@@ -10475,7 +10750,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10620,6 +10895,11 @@
       <c r="AQ56" t="inlineStr"/>
       <c r="AR56" t="inlineStr">
         <is>
+          <t>NEODAY 5MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
           <t>SKU-AB8E48CEB7BB</t>
         </is>
       </c>
@@ -10647,7 +10927,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -10796,6 +11076,11 @@
       <c r="AQ57" t="inlineStr"/>
       <c r="AR57" t="inlineStr">
         <is>
+          <t>NEODAY 10MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
           <t>SKU-24F8ECD1F980</t>
         </is>
       </c>
@@ -10823,7 +11108,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -10976,6 +11261,11 @@
       </c>
       <c r="AR58" t="inlineStr">
         <is>
+          <t>NEOMOX 125MG-5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
           <t>SKU-980A08355208</t>
         </is>
       </c>
@@ -11003,7 +11293,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11152,6 +11442,11 @@
       <c r="AQ59" t="inlineStr"/>
       <c r="AR59" t="inlineStr">
         <is>
+          <t>NEOCIPRO 500MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
           <t>SKU-9E41069E84FA</t>
         </is>
       </c>
@@ -11179,7 +11474,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11344,6 +11639,11 @@
       </c>
       <c r="AR60" t="inlineStr">
         <is>
+          <t>NEBILET 5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
           <t>SKU-53655539C54C</t>
         </is>
       </c>
@@ -11371,7 +11671,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11536,6 +11836,11 @@
       </c>
       <c r="AR61" t="inlineStr">
         <is>
+          <t>NEBIDO 1000 MG- 4 ML SOLUTION FOR INJ</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
           <t>SKU-31F22DB144DE</t>
         </is>
       </c>
@@ -11563,7 +11868,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -11720,6 +12025,11 @@
       <c r="AQ62" t="inlineStr"/>
       <c r="AR62" t="inlineStr">
         <is>
+          <t xml:space="preserve">NORACTONE </t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
           <t>SKU-575CC4DEC1BA</t>
         </is>
       </c>
@@ -11747,7 +12057,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -11908,6 +12218,11 @@
       </c>
       <c r="AR63" t="inlineStr">
         <is>
+          <t>NOOTROPIL 800 MG FILM COATED</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
           <t>SKU-7F1D9A22A2BB</t>
         </is>
       </c>
@@ -11935,7 +12250,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12086,6 +12401,11 @@
       </c>
       <c r="AR64" t="inlineStr">
         <is>
+          <t>NON PYROGENIC ACID CONC (3-023-005)I.V</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
           <t>SKU-3B529A7863AA</t>
         </is>
       </c>
@@ -12113,7 +12433,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12264,6 +12584,11 @@
       </c>
       <c r="AR65" t="inlineStr">
         <is>
+          <t>NON PYROGENIC ACID CONC (12-110-005)I.V</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
           <t>SKU-142F0EBE4306</t>
         </is>
       </c>
@@ -12291,7 +12616,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12438,6 +12763,11 @@
       <c r="AQ66" t="inlineStr"/>
       <c r="AR66" t="inlineStr">
         <is>
+          <t>NON PYROGENIC ACETATE F6(3-006-010) I.V</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
           <t>SKU-12E33E7012CF</t>
         </is>
       </c>
@@ -12465,7 +12795,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12626,6 +12956,11 @@
       </c>
       <c r="AR67" t="inlineStr">
         <is>
+          <t>NORPROLAC 75MCG TABLETS</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
           <t>SKU-7F16EE125F76</t>
         </is>
       </c>
@@ -12653,7 +12988,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -12802,6 +13137,11 @@
       <c r="AQ68" t="inlineStr"/>
       <c r="AR68" t="inlineStr">
         <is>
+          <t>NORPROLAC 25MCG-50MCG TABLETS</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
           <t>SKU-9B83B01974C6</t>
         </is>
       </c>
@@ -12829,7 +13169,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -12982,6 +13322,11 @@
       <c r="AQ69" t="inlineStr"/>
       <c r="AR69" t="inlineStr">
         <is>
+          <t>NOROXIN 400MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
           <t>SKU-6FABF1A5CC5E</t>
         </is>
       </c>
@@ -13009,7 +13354,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13166,6 +13511,11 @@
       <c r="AQ70" t="inlineStr"/>
       <c r="AR70" t="inlineStr">
         <is>
+          <t>NORMOTEN 50 MG F.C. TAB</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
           <t>SKU-86476585FBA2</t>
         </is>
       </c>
@@ -13193,7 +13543,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13354,6 +13704,11 @@
       </c>
       <c r="AR71" t="inlineStr">
         <is>
+          <t>NORMOTEN 100 MG F.C TAB</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
           <t>SKU-021CB336505E</t>
         </is>
       </c>
@@ -13381,7 +13736,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13538,6 +13893,11 @@
       <c r="AQ72" t="inlineStr"/>
       <c r="AR72" t="inlineStr">
         <is>
+          <t>NORMOTEN 100 MG F.C TAB</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
           <t>SKU-7A02EA17B1C6</t>
         </is>
       </c>
@@ -13565,7 +13925,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -13716,6 +14076,11 @@
       </c>
       <c r="AR73" t="inlineStr">
         <is>
+          <t>NON PYROGENIC ACETATE F5(3-005-010) I.V</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
           <t>SKU-49D82ED11A55</t>
         </is>
       </c>
@@ -13743,7 +14108,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -13894,6 +14259,11 @@
       </c>
       <c r="AR74" t="inlineStr">
         <is>
+          <t>NON PYROGENIC ACETATE F4(3-004-010) I.V</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
           <t>SKU-DE5C3D3C47FC</t>
         </is>
       </c>
@@ -13921,7 +14291,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14078,6 +14448,11 @@
       </c>
       <c r="AR75" t="inlineStr">
         <is>
+          <t>NIMOTOP 30MG TAB</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
           <t>SKU-728407825F29</t>
         </is>
       </c>
@@ -14105,7 +14480,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14258,6 +14633,11 @@
       <c r="AQ76" t="inlineStr"/>
       <c r="AR76" t="inlineStr">
         <is>
+          <t>NICOTINELL 1MG LOZENGES</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
           <t>SKU-333D4FB4C842</t>
         </is>
       </c>
@@ -14285,7 +14665,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14446,6 +14826,11 @@
       <c r="AQ77" t="inlineStr"/>
       <c r="AR77" t="inlineStr">
         <is>
+          <t>NITRODERM TTS 5 PATCHES</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
           <t>SKU-724F8062279A</t>
         </is>
       </c>
@@ -14473,7 +14858,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -14626,6 +15011,11 @@
       </c>
       <c r="AR78" t="inlineStr">
         <is>
+          <t>NOMAL 50 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
           <t>SKU-453367701D12</t>
         </is>
       </c>
@@ -14653,7 +15043,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -14814,6 +15204,11 @@
       </c>
       <c r="AR79" t="inlineStr">
         <is>
+          <t>NOLVADEX-D TAB 20MG</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
           <t>SKU-BF45252CBE3E</t>
         </is>
       </c>
@@ -14841,7 +15236,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -14998,6 +15393,11 @@
       <c r="AQ80" t="inlineStr"/>
       <c r="AR80" t="inlineStr">
         <is>
+          <t>NOLVADEX 10 MG TABs</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
           <t>SKU-E898AC8F18A5</t>
         </is>
       </c>
@@ -15025,7 +15425,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15168,6 +15568,11 @@
       <c r="AQ81" t="inlineStr"/>
       <c r="AR81" t="inlineStr">
         <is>
+          <t>NON PYROGENIC ACETATE F3(3-003-010) I.V</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
           <t>SKU-3F443DB295E4</t>
         </is>
       </c>
@@ -15195,7 +15600,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15356,6 +15761,11 @@
       </c>
       <c r="AR82" t="inlineStr">
         <is>
+          <t>NIZORAL CREAM 2%</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
           <t>SKU-7BFC4A67F059</t>
         </is>
       </c>
@@ -15383,7 +15793,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -15544,6 +15954,11 @@
       <c r="AQ83" t="inlineStr"/>
       <c r="AR83" t="inlineStr">
         <is>
+          <t>NITRODERM TTS-10 SYSTEM</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
           <t>SKU-DFABC3F0A73A</t>
         </is>
       </c>
@@ -15571,7 +15986,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -15728,6 +16143,11 @@
       </c>
       <c r="AR84" t="inlineStr">
         <is>
+          <t>NITRODERM TTS-10 SYSTEM</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
           <t>SKU-9E114C68477A</t>
         </is>
       </c>
@@ -15755,7 +16175,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -15920,6 +16340,11 @@
       </c>
       <c r="AR85" t="inlineStr">
         <is>
+          <t>NITRODERM TTS 5 PATCHES</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
           <t>SKU-9FEB062BB11F</t>
         </is>
       </c>
@@ -15947,7 +16372,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16104,6 +16529,11 @@
       <c r="AQ86" t="inlineStr"/>
       <c r="AR86" t="inlineStr">
         <is>
+          <t>MYFORTIC 360 MG E.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
           <t>SKU-EF9AC44C49AF</t>
         </is>
       </c>
@@ -16131,7 +16561,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16284,6 +16714,11 @@
       </c>
       <c r="AR87" t="inlineStr">
         <is>
+          <t>MYDRIACYL 1% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
           <t>SKU-21291665E9DF</t>
         </is>
       </c>
@@ -16311,7 +16746,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16476,6 +16911,11 @@
       </c>
       <c r="AR88" t="inlineStr">
         <is>
+          <t>MYDFRIN 2.5% DROPS</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
           <t>SKU-A65C63BF79DB</t>
         </is>
       </c>
@@ -16503,7 +16943,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -16664,6 +17104,11 @@
       </c>
       <c r="AR89" t="inlineStr">
         <is>
+          <t>MILK OF MAGNESIA SUSP.</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
           <t>SKU-63AD5F9CEADB</t>
         </is>
       </c>
@@ -16691,7 +17136,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16848,6 +17293,11 @@
       </c>
       <c r="AR90" t="inlineStr">
         <is>
+          <t>MIDROXIL 500MG\5ML SUSP.</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
           <t>SKU-03A7034369F3</t>
         </is>
       </c>
@@ -16875,7 +17325,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17028,6 +17478,11 @@
       <c r="AQ91" t="inlineStr"/>
       <c r="AR91" t="inlineStr">
         <is>
+          <t>MIDROXIL 500 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
           <t>SKU-9F18ACC42F5A</t>
         </is>
       </c>
@@ -17055,7 +17510,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17212,6 +17667,11 @@
       </c>
       <c r="AR92" t="inlineStr">
         <is>
+          <t>MIDROXIL 250MG\5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
           <t>SKU-F9CF05706219</t>
         </is>
       </c>
@@ -17239,7 +17699,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17392,6 +17852,11 @@
       <c r="AQ93" t="inlineStr"/>
       <c r="AR93" t="inlineStr">
         <is>
+          <t>MIDRONE EXTRA TAB</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
           <t>SKU-1E608F214E77</t>
         </is>
       </c>
@@ -17419,7 +17884,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -17572,6 +18037,11 @@
       <c r="AQ94" t="inlineStr"/>
       <c r="AR94" t="inlineStr">
         <is>
+          <t>MIDAFLEX 500MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
           <t>SKU-71CBEAC75BAD</t>
         </is>
       </c>
@@ -17599,7 +18069,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -17752,6 +18222,11 @@
       <c r="AQ95" t="inlineStr"/>
       <c r="AR95" t="inlineStr">
         <is>
+          <t>MIDAFLEX 250 mg capsule</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
           <t>SKU-0816BF3751DF</t>
         </is>
       </c>
@@ -17779,7 +18254,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -17936,6 +18411,11 @@
       </c>
       <c r="AR96" t="inlineStr">
         <is>
+          <t>MIDAFLEX 250 mg oral suspension</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
           <t>SKU-29FAF9917077</t>
         </is>
       </c>
@@ -17963,7 +18443,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18116,6 +18596,11 @@
       <c r="AQ97" t="inlineStr"/>
       <c r="AR97" t="inlineStr">
         <is>
+          <t>MIDAFLEX 125MG-5MLSUSP</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
           <t>SKU-C702A02D98C2</t>
         </is>
       </c>
@@ -18143,7 +18628,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18296,6 +18781,11 @@
       <c r="AQ98" t="inlineStr"/>
       <c r="AR98" t="inlineStr">
         <is>
+          <t>MICOVER- H CREAM</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
           <t>SKU-1BD08A81E0F9</t>
         </is>
       </c>
@@ -18323,7 +18813,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -18476,6 +18966,11 @@
       </c>
       <c r="AR99" t="inlineStr">
         <is>
+          <t>MICOVER 2% CREAM</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
           <t>SKU-E8FA719E3341</t>
         </is>
       </c>
@@ -18503,7 +18998,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -18664,6 +19159,11 @@
       <c r="AQ100" t="inlineStr"/>
       <c r="AR100" t="inlineStr">
         <is>
+          <t>MICONAZ 2% POWDER</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
           <t>SKU-468B84349922</t>
         </is>
       </c>
@@ -18691,7 +19191,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -18839,6 +19339,11 @@
       </c>
       <c r="AQ101" t="inlineStr"/>
       <c r="AR101" t="inlineStr">
+        <is>
+          <t>MIMPARA 30MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
         <is>
           <t>SKU-8BD3B2FE1702</t>
         </is>
@@ -18855,7 +19360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18901,100 +19406,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19026,7 +19536,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19041,92 +19551,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-71918</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>32.83</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>474</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19158,7 +19673,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19173,92 +19688,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-98669</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>378.4</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>475</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19290,7 +19810,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19305,92 +19825,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-75131</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>353.99</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>476</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19422,7 +19947,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19437,92 +19962,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-51395</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>218.96</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>477</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19554,7 +20084,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -19569,92 +20099,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-24448</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>113.79</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>478</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19686,7 +20221,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -19701,92 +20236,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-94659</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>250.32</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>479</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19818,7 +20358,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -19833,92 +20373,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-91438</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>51.1</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>480</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19950,7 +20495,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -19965,92 +20510,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-68823</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>28.87</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>481</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20082,7 +20632,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20097,92 +20647,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-85724</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>240.63</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>482</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20214,7 +20769,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20229,92 +20784,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-80398</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>359.44</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>483</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20346,7 +20906,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20361,92 +20921,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-77011</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>333.25</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>484</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20478,7 +21043,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -20493,92 +21058,97 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>SKU-33561</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>353.96</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T13" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U13" t="inlineStr">
+      <c r="U13" t="n">
+        <v>485</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>100</v>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>12</v>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20595,7 +21165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20701,6 +21271,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -20736,7 +21316,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -20801,6 +21381,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-DEFBDC36A070</t>
         </is>
@@ -20837,7 +21427,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -20902,6 +21492,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-676116B67795</t>
         </is>
@@ -20938,7 +21538,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21003,6 +21603,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-0AF61003C987</t>
         </is>
@@ -21039,7 +21649,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21104,6 +21714,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-0ADAFE4A7EA9</t>
         </is>
@@ -21140,7 +21760,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21205,6 +21825,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-E6A8758B9A31</t>
         </is>
@@ -21241,7 +21871,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21306,6 +21936,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-B0B0D7805A48</t>
         </is>
@@ -21342,7 +21982,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21407,6 +22047,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-9E96208AF921</t>
         </is>
@@ -21443,7 +22093,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21508,6 +22158,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-BA3DCAE141D7</t>
         </is>
@@ -21544,7 +22204,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -21609,6 +22269,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-C40AD86AE9E6</t>
         </is>
@@ -21645,7 +22315,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -21710,6 +22380,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-0AA96092FA26</t>
         </is>
@@ -21746,7 +22426,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -21811,6 +22491,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-93513B69404D</t>
         </is>
@@ -21847,7 +22537,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -21912,6 +22602,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-9EEDB0A9CA4E</t>
         </is>
@@ -21948,7 +22648,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22013,6 +22713,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-D9CB5785A275</t>
         </is>
@@ -22049,7 +22759,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22114,6 +22824,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-38E2C9E7A880</t>
         </is>
@@ -22150,7 +22870,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22215,6 +22935,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-EEAECC24678A</t>
         </is>
@@ -22251,7 +22981,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22316,6 +23046,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-2EDB12EB621D</t>
         </is>
@@ -22352,7 +23092,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22417,6 +23157,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-6D5443504327</t>
         </is>
@@ -22453,7 +23203,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22518,6 +23268,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-4174A6B5BA78</t>
         </is>
@@ -22554,7 +23314,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -22619,6 +23379,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-A045942982EE</t>
         </is>
@@ -22655,7 +23425,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -22720,6 +23490,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-E40320B2F164</t>
         </is>

--- a/product_upload/packages/5/file.xlsx
+++ b/product_upload/packages/5/file.xlsx
@@ -1629,8 +1629,16 @@
           <t>7000000736-30-100000073375</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>LONZET 30MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1814,8 +1822,16 @@
           <t>7000000736-15-100000073375</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>LONZET 15MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -1995,8 +2011,16 @@
           <t>7000000773-1-100000073652</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>LOHIST 5 MG-5 ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2176,8 +2200,16 @@
           <t>7000000773-10-100000073664</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>LOHIST 10 MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2361,8 +2393,16 @@
           <t>7000000068-5-100000073664</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>LOFRAL 5MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2546,8 +2586,16 @@
           <t>7000000068-10-100000073664</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>LOFRAL 10MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2731,8 +2779,16 @@
           <t>7000000629-0.1-100000073713</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>LOCOID OINT 0.1% detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -3298,8 +3354,16 @@
           <t>7000000766-10-100000073664</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>LINOPRIL 10MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3668,8 +3732,16 @@
           <t>7000000766-20-100000073664</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>LINOPRIL 20MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -3857,8 +3929,16 @@
           <t>7000000766-5-100000073664</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>LINOPRIL 5MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4042,8 +4122,16 @@
           <t>7000000539-20-100000073375</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>LINZ 20 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4223,8 +4311,16 @@
           <t>7000000758-2-100000073726</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>LIOCAINE 2% GEL detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -5369,8 +5465,16 @@
           <t>7000001052-300-100000073375</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>NERVAX 300MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5739,8 +5843,16 @@
           <t>7000000851-2-200000002007</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>NEOXIDIL 2% SOLN. detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -5928,8 +6040,16 @@
           <t>7000000803-7.5-100000073664</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>NEOXICAM 7.5MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6109,8 +6229,16 @@
           <t>7000000803-15-100000073664</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>NEOXICAM 15MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6286,8 +6414,16 @@
           <t>7000001127-0.4-100000073652</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>NEOVENTIL 2MG-5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6467,8 +6603,16 @@
           <t>7000000015-25-100000073375</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>NEOTIGASON 25MG CAPS detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -6652,8 +6796,16 @@
           <t>7000000015-10-100000073375</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>NEOTIGASON 10MG CAPS detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -7018,8 +7170,16 @@
           <t>7000000364-0.5-100000073652</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>NEORIN 2.5MG -5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7388,8 +7548,16 @@
           <t>21000002635-201-100000073863</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>NEUROBION ampoules detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -7573,8 +7741,16 @@
           <t>7000000867--100000073664</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>NEUROTRAT FORTE TAB. detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -8520,8 +8696,16 @@
           <t>7000000561-300-100000073375</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>NEURONTIN detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -8890,8 +9074,16 @@
           <t>7000000072-50-100000073649</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>NEOMOX 250MG-5ML SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9075,8 +9267,16 @@
           <t>7000000961-24-200000016419</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>NEOMOL 120MG-5ML SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9256,8 +9456,16 @@
           <t>7000000879-500-100000073664</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>NAPROX D.S 500MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -10207,8 +10415,16 @@
           <t>8000000552--100000073713</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>NEO-HAEMORRHAN OINT detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10386,8 +10602,16 @@
           <t>8000000551--100000073843</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>NEO-HAEMORRHAN SUPP. detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -10758,8 +10982,16 @@
           <t>7000000773-1-100000073652</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>NEODAY 5MG-5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -10935,8 +11167,16 @@
           <t>7000000773-10-100000073664</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>NEODAY 10MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11116,8 +11356,16 @@
           <t>7000000072-25-100000073649</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>NEOMOX 125MG-5ML SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11301,8 +11549,16 @@
           <t>7000000286-500-100000073665</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>NEOCIPRO 500MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -12258,8 +12514,16 @@
           <t>8000000613--200000002007</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>NON PYROGENIC ACID CONC (3-023-005)I.V detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12441,8 +12705,16 @@
           <t>8000000613--200000002007</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>NON PYROGENIC ACID CONC (12-110-005)I.V detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -12624,8 +12896,16 @@
           <t>8000000607--200000002007</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>NON PYROGENIC ACETATE F6(3-006-010) I.V detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -12996,8 +13276,16 @@
           <t>7000001076-0.0273-100000073664</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>NORPROLAC 25MCG-50MCG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13933,8 +14221,16 @@
           <t>8000000608--200000002007</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>NON PYROGENIC ACETATE F5(3-005-010) I.V detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -14116,8 +14412,16 @@
           <t>8000000608--200000002007</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>NON PYROGENIC ACETATE F4(3-004-010) I.V detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -14299,8 +14603,16 @@
           <t>7000000895-30-100000073664</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>NIMOTOP 30MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -14488,8 +14800,16 @@
           <t>7000001829-1-100000073703</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>NICOTINELL 1MG LOZENGES detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -14866,8 +15186,16 @@
           <t>7000001265-50-200000016452</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>NOMAL 50 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -15433,8 +15761,16 @@
           <t>8000000608--200000002007</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>NON PYROGENIC ACETATE F3(3-003-010) I.V detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -15994,8 +16330,16 @@
           <t>7000002634-50-100000073741</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>NITRODERM TTS-10 SYSTEM detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16569,8 +16913,16 @@
           <t>7000001286-1-100000073759</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>MYDRIACYL 1% EYE DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -16951,8 +17303,16 @@
           <t>7000000786-415-200000016419</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>MILK OF MAGNESIA SUSP. detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17144,8 +17504,16 @@
           <t>7000000227-100-100000073362</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>MIDROXIL 500MG\5ML SUSP. detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17333,8 +17701,16 @@
           <t>7000000227-500-200000016452</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>MIDROXIL 500 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -17518,8 +17894,16 @@
           <t>7000000227-50-100000073362</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>MIDROXIL 250MG\5ML SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -17707,8 +18091,16 @@
           <t>14000001151-560-100000073664</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>MIDRONE EXTRA TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -17892,8 +18284,16 @@
           <t>7000000228-500-200000016452</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>MIDAFLEX 500MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18077,8 +18477,16 @@
           <t>7000000228-250-200000016452</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>MIDAFLEX 250 mg capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -18262,8 +18670,16 @@
           <t>7000000228-50-100000073362</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>MIDAFLEX 250 mg oral suspension detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -18451,8 +18867,16 @@
           <t>7000000228-25-100000073362</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>MIDAFLEX 125MG-5MLSUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -18636,8 +19060,16 @@
           <t>14000001471-2.2-100000073712</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>MICOVER- H CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -18821,8 +19253,16 @@
           <t>7000000844-2-100000073712</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>MICOVER 2% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -19199,8 +19639,16 @@
           <t>7000000282-30-100000073665</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>MIMPARA 30MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/5/file.xlsx
+++ b/product_upload/packages/5/file.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -21613,7 +21613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21694,40 +21694,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -21807,38 +21812,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>272.96</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-DEFBDC36A070</t>
         </is>
@@ -21918,38 +21928,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>426.93</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-676116B67795</t>
         </is>
@@ -22029,38 +22044,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>460.41</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-0AF61003C987</t>
         </is>
@@ -22140,38 +22160,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>132.28</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-0ADAFE4A7EA9</t>
         </is>
@@ -22251,38 +22276,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>70.11</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-E6A8758B9A31</t>
         </is>
@@ -22362,38 +22392,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>56.98</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-B0B0D7805A48</t>
         </is>
@@ -22473,38 +22508,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>186.59</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-9E96208AF921</t>
         </is>
@@ -22584,38 +22624,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>360.06</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-BA3DCAE141D7</t>
         </is>
@@ -22695,38 +22740,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>227</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-C40AD86AE9E6</t>
         </is>
@@ -22806,38 +22856,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>311.82</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-0AA96092FA26</t>
         </is>
@@ -22917,38 +22972,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>245.47</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-93513B69404D</t>
         </is>
@@ -23028,38 +23088,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>352.18</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-9EEDB0A9CA4E</t>
         </is>
@@ -23139,38 +23204,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>257.67</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-D9CB5785A275</t>
         </is>
@@ -23250,38 +23320,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>383.21</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-38E2C9E7A880</t>
         </is>
@@ -23361,38 +23436,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>271.1</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-EEAECC24678A</t>
         </is>
@@ -23472,38 +23552,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>210.36</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-2EDB12EB621D</t>
         </is>
@@ -23583,38 +23668,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>25.79</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-6D5443504327</t>
         </is>
@@ -23694,38 +23784,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>405.3</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-4174A6B5BA78</t>
         </is>
@@ -23805,38 +23900,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>202.12</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-A045942982EE</t>
         </is>
@@ -23916,38 +24016,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>470.82</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-E40320B2F164</t>
         </is>
